--- a/automation/reports/excel/Failed_Test_Cases.xlsx
+++ b/automation/reports/excel/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
   <si>
     <t>Test ID</t>
   </si>
@@ -34,73 +34,151 @@
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>TC_VAL_014</t>
+    <t>TC_AUTH_020</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Authentication Verification - Case 20</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 19</t>
+  </si>
+  <si>
+    <t>TC_AUTH_023</t>
+  </si>
+  <si>
+    <t>Authentication Verification - Case 23</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 22</t>
+  </si>
+  <si>
+    <t>TC_PROF_002</t>
+  </si>
+  <si>
+    <t>Profile Management</t>
+  </si>
+  <si>
+    <t>Profile Management Verification - Case 2</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 91</t>
+  </si>
+  <si>
+    <t>TC_FORM_037</t>
+  </si>
+  <si>
+    <t>Forms</t>
+  </si>
+  <si>
+    <t>Forms Verification - Case 37</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 196</t>
+  </si>
+  <si>
+    <t>TC_SRCH_001</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Search Verification - Case 1</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 240</t>
+  </si>
+  <si>
+    <t>TC_SRCH_008</t>
+  </si>
+  <si>
+    <t>Search Verification - Case 8</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 247</t>
+  </si>
+  <si>
+    <t>TC_FILT_013</t>
+  </si>
+  <si>
+    <t>Filters</t>
+  </si>
+  <si>
+    <t>Filters Verification - Case 13</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 272</t>
+  </si>
+  <si>
+    <t>TC_VAL_036</t>
   </si>
   <si>
     <t>Input Validation</t>
   </si>
   <si>
-    <t>Input Validation Verification - Case 14</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 293</t>
-  </si>
-  <si>
-    <t>TC_ERR_001</t>
-  </si>
-  <si>
-    <t>Error Handling</t>
-  </si>
-  <si>
-    <t>Error Handling Verification - Case 1</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 320</t>
-  </si>
-  <si>
-    <t>TC_SESS_010</t>
+    <t>Input Validation Verification - Case 36</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 315</t>
+  </si>
+  <si>
+    <t>TC_SESS_003</t>
   </si>
   <si>
     <t>Session Management</t>
   </si>
   <si>
-    <t>Session Management Verification - Case 10</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 349</t>
-  </si>
-  <si>
-    <t>TC_PERF_017</t>
-  </si>
-  <si>
-    <t>Performance Smoke Tests</t>
-  </si>
-  <si>
-    <t>Performance Smoke Tests Verification - Case 17</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 456</t>
-  </si>
-  <si>
-    <t>TC_REGR_001</t>
+    <t>Session Management Verification - Case 3</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 342</t>
+  </si>
+  <si>
+    <t>TC_SESS_009</t>
+  </si>
+  <si>
+    <t>Session Management Verification - Case 9</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 348</t>
+  </si>
+  <si>
+    <t>TC_NOTIF_016</t>
+  </si>
+  <si>
+    <t>Notifications</t>
+  </si>
+  <si>
+    <t>Notifications Verification - Case 16</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 375</t>
+  </si>
+  <si>
+    <t>TC_REGR_017</t>
   </si>
   <si>
     <t>Regression Suite</t>
   </si>
   <si>
-    <t>Regression Suite Verification - Case 1</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 460</t>
+    <t>Regression Suite Verification - Case 17</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 476</t>
   </si>
 </sst>
 </file>
@@ -491,11 +569,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
@@ -542,7 +620,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>109</v>
+        <v>233</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -553,91 +631,252 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>156</v>
+      </c>
+      <c r="G3" t="s">
         <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>254</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>230</v>
+      </c>
+      <c r="G4" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4">
-        <v>296</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>161</v>
+      </c>
+      <c r="G5" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>180</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>252</v>
+      </c>
+      <c r="G6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>202</v>
-      </c>
-      <c r="G6" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>262</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>114</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9">
+        <v>104</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10">
+        <v>132</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11">
+        <v>187</v>
+      </c>
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12">
+        <v>227</v>
+      </c>
+      <c r="G12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13">
+        <v>134</v>
+      </c>
+      <c r="G13" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/automation/reports/excel/Failed_Test_Cases.xlsx
+++ b/automation/reports/excel/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Test ID</t>
   </si>
@@ -34,151 +34,37 @@
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>TC_AUTH_020</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Authentication Verification - Case 20</t>
-  </si>
-  <si>
-    <t>Low</t>
+    <t>TC_VAL_012</t>
+  </si>
+  <si>
+    <t>Input Validation</t>
+  </si>
+  <si>
+    <t>Input Validation Verification - Case 12</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
   <si>
     <t>FAILED</t>
   </si>
   <si>
-    <t>AssertionError: State mismatch on scenario index 19</t>
-  </si>
-  <si>
-    <t>TC_AUTH_023</t>
-  </si>
-  <si>
-    <t>Authentication Verification - Case 23</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 22</t>
-  </si>
-  <si>
-    <t>TC_PROF_002</t>
-  </si>
-  <si>
-    <t>Profile Management</t>
-  </si>
-  <si>
-    <t>Profile Management Verification - Case 2</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 91</t>
-  </si>
-  <si>
-    <t>TC_FORM_037</t>
-  </si>
-  <si>
-    <t>Forms</t>
-  </si>
-  <si>
-    <t>Forms Verification - Case 37</t>
+    <t>AssertionError: State mismatch on scenario index 291</t>
+  </si>
+  <si>
+    <t>TC_SESS_001</t>
+  </si>
+  <si>
+    <t>Session Management</t>
+  </si>
+  <si>
+    <t>Session Management Verification - Case 1</t>
   </si>
   <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>AssertionError: State mismatch on scenario index 196</t>
-  </si>
-  <si>
-    <t>TC_SRCH_001</t>
-  </si>
-  <si>
-    <t>Search</t>
-  </si>
-  <si>
-    <t>Search Verification - Case 1</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 240</t>
-  </si>
-  <si>
-    <t>TC_SRCH_008</t>
-  </si>
-  <si>
-    <t>Search Verification - Case 8</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 247</t>
-  </si>
-  <si>
-    <t>TC_FILT_013</t>
-  </si>
-  <si>
-    <t>Filters</t>
-  </si>
-  <si>
-    <t>Filters Verification - Case 13</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 272</t>
-  </si>
-  <si>
-    <t>TC_VAL_036</t>
-  </si>
-  <si>
-    <t>Input Validation</t>
-  </si>
-  <si>
-    <t>Input Validation Verification - Case 36</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 315</t>
-  </si>
-  <si>
-    <t>TC_SESS_003</t>
-  </si>
-  <si>
-    <t>Session Management</t>
-  </si>
-  <si>
-    <t>Session Management Verification - Case 3</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 342</t>
-  </si>
-  <si>
-    <t>TC_SESS_009</t>
-  </si>
-  <si>
-    <t>Session Management Verification - Case 9</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 348</t>
-  </si>
-  <si>
-    <t>TC_NOTIF_016</t>
-  </si>
-  <si>
-    <t>Notifications</t>
-  </si>
-  <si>
-    <t>Notifications Verification - Case 16</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 375</t>
-  </si>
-  <si>
-    <t>TC_REGR_017</t>
-  </si>
-  <si>
-    <t>Regression Suite</t>
-  </si>
-  <si>
-    <t>Regression Suite Verification - Case 17</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 476</t>
+    <t>AssertionError: State mismatch on scenario index 340</t>
   </si>
 </sst>
 </file>
@@ -569,10 +455,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
@@ -620,7 +506,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -631,252 +517,22 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
         <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4">
-        <v>230</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>161</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>252</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>262</v>
-      </c>
-      <c r="G7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>114</v>
-      </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9">
-        <v>104</v>
-      </c>
-      <c r="G9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10">
-        <v>132</v>
-      </c>
-      <c r="G10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11">
-        <v>187</v>
-      </c>
-      <c r="G11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12">
-        <v>227</v>
-      </c>
-      <c r="G12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13">
-        <v>134</v>
-      </c>
-      <c r="G13" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/automation/reports/excel/Failed_Test_Cases.xlsx
+++ b/automation/reports/excel/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>Test ID</t>
   </si>
@@ -34,37 +34,76 @@
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>TC_VAL_012</t>
+    <t>TC_AZ_019</t>
+  </si>
+  <si>
+    <t>Authorization</t>
+  </si>
+  <si>
+    <t>Authorization Verification - Case 19</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 58</t>
+  </si>
+  <si>
+    <t>TC_REG_003</t>
+  </si>
+  <si>
+    <t>Registration</t>
+  </si>
+  <si>
+    <t>Registration Verification - Case 3</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 72</t>
+  </si>
+  <si>
+    <t>TC_VAL_002</t>
   </si>
   <si>
     <t>Input Validation</t>
   </si>
   <si>
-    <t>Input Validation Verification - Case 12</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 291</t>
-  </si>
-  <si>
-    <t>TC_SESS_001</t>
-  </si>
-  <si>
-    <t>Session Management</t>
-  </si>
-  <si>
-    <t>Session Management Verification - Case 1</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 340</t>
+    <t>Input Validation Verification - Case 2</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 281</t>
+  </si>
+  <si>
+    <t>TC_ACC_001</t>
+  </si>
+  <si>
+    <t>Accessibility</t>
+  </si>
+  <si>
+    <t>Accessibility Verification - Case 1</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 410</t>
+  </si>
+  <si>
+    <t>TC_REGR_001</t>
+  </si>
+  <si>
+    <t>Regression Suite</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 1</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 460</t>
   </si>
 </sst>
 </file>
@@ -455,11 +494,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
@@ -506,7 +545,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -529,10 +568,79 @@
         <v>11</v>
       </c>
       <c r="F3">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>267</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>255</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>151</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/automation/reports/excel/Failed_Test_Cases.xlsx
+++ b/automation/reports/excel/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>Test ID</t>
   </si>
@@ -34,13 +34,13 @@
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>TC_AZ_019</t>
-  </si>
-  <si>
-    <t>Authorization</t>
-  </si>
-  <si>
-    <t>Authorization Verification - Case 19</t>
+    <t>TC_NAV_004</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Navigation Verification - Case 4</t>
   </si>
   <si>
     <t>Medium</t>
@@ -49,61 +49,118 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>AssertionError: State mismatch on scenario index 58</t>
-  </si>
-  <si>
-    <t>TC_REG_003</t>
-  </si>
-  <si>
-    <t>Registration</t>
-  </si>
-  <si>
-    <t>Registration Verification - Case 3</t>
+    <t>AssertionError: State mismatch on scenario index 113</t>
+  </si>
+  <si>
+    <t>TC_NAV_005</t>
+  </si>
+  <si>
+    <t>Navigation Verification - Case 5</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 114</t>
+  </si>
+  <si>
+    <t>TC_DASH_010</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Dashboard Verification - Case 10</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 149</t>
+  </si>
+  <si>
+    <t>TC_FORM_008</t>
+  </si>
+  <si>
+    <t>Forms</t>
+  </si>
+  <si>
+    <t>Forms Verification - Case 8</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 167</t>
+  </si>
+  <si>
+    <t>TC_CRUD_019</t>
+  </si>
+  <si>
+    <t>CRUD Operations</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 19</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 218</t>
+  </si>
+  <si>
+    <t>TC_SRCH_005</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Search Verification - Case 5</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 244</t>
+  </si>
+  <si>
+    <t>TC_FILT_010</t>
+  </si>
+  <si>
+    <t>Filters</t>
+  </si>
+  <si>
+    <t>Filters Verification - Case 10</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 269</t>
+  </si>
+  <si>
+    <t>TC_ERR_009</t>
+  </si>
+  <si>
+    <t>Error Handling</t>
+  </si>
+  <si>
+    <t>Error Handling Verification - Case 9</t>
   </si>
   <si>
     <t>High</t>
   </si>
   <si>
-    <t>AssertionError: State mismatch on scenario index 72</t>
-  </si>
-  <si>
-    <t>TC_VAL_002</t>
-  </si>
-  <si>
-    <t>Input Validation</t>
-  </si>
-  <si>
-    <t>Input Validation Verification - Case 2</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 281</t>
-  </si>
-  <si>
-    <t>TC_ACC_001</t>
-  </si>
-  <si>
-    <t>Accessibility</t>
-  </si>
-  <si>
-    <t>Accessibility Verification - Case 1</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 410</t>
-  </si>
-  <si>
-    <t>TC_REGR_001</t>
-  </si>
-  <si>
-    <t>Regression Suite</t>
-  </si>
-  <si>
-    <t>Regression Suite Verification - Case 1</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 460</t>
+    <t>AssertionError: State mismatch on scenario index 328</t>
+  </si>
+  <si>
+    <t>TC_SESS_017</t>
+  </si>
+  <si>
+    <t>Session Management</t>
+  </si>
+  <si>
+    <t>Session Management Verification - Case 17</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 356</t>
+  </si>
+  <si>
+    <t>TC_UPL_018</t>
+  </si>
+  <si>
+    <t>File Upload</t>
+  </si>
+  <si>
+    <t>File Upload Verification - Case 18</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 397</t>
   </si>
 </sst>
 </file>
@@ -494,11 +551,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
@@ -545,7 +602,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -556,79 +613,79 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>183</v>
+      </c>
+      <c r="G3" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>215</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>170</v>
+      </c>
+      <c r="G4" t="s">
         <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4">
-        <v>267</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>186</v>
+      </c>
+      <c r="G5" t="s">
         <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>255</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -637,10 +694,125 @@
         <v>11</v>
       </c>
       <c r="F6">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="G6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
         <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>111</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>140</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9">
+        <v>211</v>
+      </c>
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10">
+        <v>122</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11">
+        <v>155</v>
+      </c>
+      <c r="G11" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
